--- a/data/processed/expomap_portal/downloads/household-expo-autumn-2026-normalized-public.xlsx
+++ b/data/processed/expomap_portal/downloads/household-expo-autumn-2026-normalized-public.xlsx
@@ -685,12 +685,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:29Z</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:29Z</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:29Z</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:29Z</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:29Z</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:29Z</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:30Z</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:30Z</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:30Z</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:30Z</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:24Z</t>
+          <t>2026-08-24T05:47:30Z</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:30Z</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:30Z</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:31Z</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:29Z</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:31Z</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:31Z</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:31Z</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:11Z</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:31Z</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:31Z</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:31Z</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:25Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:20Z</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:11Z</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:32Z</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:20Z</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:26Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:33Z</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:54Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:34Z</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:35Z</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:27Z</t>
+          <t>2026-08-24T05:47:35Z</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:54Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:35Z</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:35Z</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:35Z</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:36Z</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:36Z</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:36Z</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:36Z</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:36Z</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:36Z</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:37Z</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:28Z</t>
+          <t>2026-08-24T05:47:37Z</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:37Z</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:36Z</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:37Z</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -9368,12 +9368,12 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:38Z</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:37Z</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:54Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:38Z</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:37Z</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:37Z</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:38Z</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:38Z</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -10249,12 +10249,12 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:38Z</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:38Z</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:29Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:39Z</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:40Z</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
@@ -11690,12 +11690,12 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:30Z</t>
+          <t>2026-08-24T05:47:40Z</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:40Z</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:40Z</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:41Z</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:41Z</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:41Z</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -12357,12 +12357,12 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:41Z</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:40Z</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -12581,12 +12581,12 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:41Z</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -12688,12 +12688,12 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:54Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:41Z</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12912,12 +12912,12 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:31Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13462,12 +13462,12 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -13691,12 +13691,12 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:10Z</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13798,12 +13798,12 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:42Z</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:32Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -14358,12 +14358,12 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:11Z</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
@@ -14465,12 +14465,12 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
@@ -14577,12 +14577,12 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:54Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
@@ -14908,12 +14908,12 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -15453,12 +15453,12 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:43Z</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
@@ -15565,12 +15565,12 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:44Z</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -15677,12 +15677,12 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:44Z</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:44Z</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:33Z</t>
+          <t>2026-08-24T05:47:44Z</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
@@ -16003,12 +16003,12 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:44Z</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
@@ -16115,12 +16115,12 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:45Z</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
@@ -16227,12 +16227,12 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:45Z</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:45Z</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
@@ -16441,12 +16441,12 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:45Z</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
@@ -16553,12 +16553,12 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:45Z</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:45Z</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
@@ -16777,12 +16777,12 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
@@ -16889,12 +16889,12 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
@@ -17113,12 +17113,12 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
@@ -17225,12 +17225,12 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
@@ -17337,12 +17337,12 @@
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:34Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
@@ -17444,12 +17444,12 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
@@ -17658,12 +17658,12 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X156" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:46Z</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:47Z</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
@@ -17989,12 +17989,12 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:47Z</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X159" t="inlineStr">
@@ -18096,12 +18096,12 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:47Z</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X160" t="inlineStr">
@@ -18208,12 +18208,12 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:47Z</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
@@ -18320,12 +18320,12 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:47Z</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
@@ -18427,12 +18427,12 @@
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:47Z</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X163" t="inlineStr">
@@ -18534,12 +18534,12 @@
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:35Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X164" t="inlineStr">
@@ -18646,12 +18646,12 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X165" t="inlineStr">
@@ -18758,12 +18758,12 @@
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
@@ -18870,12 +18870,12 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
@@ -18972,12 +18972,12 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X168" t="inlineStr">
@@ -19079,12 +19079,12 @@
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X169" t="inlineStr">
@@ -19191,12 +19191,12 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X170" t="inlineStr">
@@ -19308,12 +19308,12 @@
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:11Z</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X171" t="inlineStr">
@@ -19415,12 +19415,12 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
@@ -19527,12 +19527,12 @@
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:48Z</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
@@ -19639,12 +19639,12 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:49Z</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X174" t="inlineStr">
@@ -19751,12 +19751,12 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:49Z</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
@@ -19863,12 +19863,12 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:49Z</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X176" t="inlineStr">
@@ -19970,12 +19970,12 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:49Z</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
@@ -20082,12 +20082,12 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:49Z</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X178" t="inlineStr">
@@ -20179,12 +20179,12 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:49Z</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
@@ -20291,12 +20291,12 @@
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:36Z</t>
+          <t>2026-08-24T05:47:50Z</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
@@ -20515,12 +20515,12 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:50Z</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
@@ -20622,12 +20622,12 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:50Z</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
@@ -20734,12 +20734,12 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:50Z</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
@@ -20846,12 +20846,12 @@
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:50Z</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
@@ -20953,12 +20953,12 @@
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
@@ -21065,12 +21065,12 @@
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
@@ -21177,12 +21177,12 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
@@ -21284,12 +21284,12 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
@@ -21396,12 +21396,12 @@
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X190" t="inlineStr">
@@ -21508,12 +21508,12 @@
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
@@ -21615,12 +21615,12 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
@@ -21727,12 +21727,12 @@
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
@@ -21839,12 +21839,12 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
@@ -21951,12 +21951,12 @@
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:51Z</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
@@ -22063,12 +22063,12 @@
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
@@ -22277,12 +22277,12 @@
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X198" t="inlineStr">
@@ -22389,12 +22389,12 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
@@ -22496,12 +22496,12 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
@@ -22720,12 +22720,12 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:38Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
@@ -22832,12 +22832,12 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X203" t="inlineStr">
@@ -22944,12 +22944,12 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:52Z</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X204" t="inlineStr">
@@ -23056,12 +23056,12 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:53Z</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X205" t="inlineStr">
@@ -23168,12 +23168,12 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:53Z</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
@@ -23280,12 +23280,12 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:53Z</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
@@ -23392,12 +23392,12 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X208" t="inlineStr">
@@ -23504,12 +23504,12 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
@@ -23728,12 +23728,12 @@
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
@@ -23840,12 +23840,12 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
@@ -23952,12 +23952,12 @@
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:39Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X213" t="inlineStr">
@@ -24064,12 +24064,12 @@
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
@@ -24176,12 +24176,12 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
@@ -24288,12 +24288,12 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:54Z</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
@@ -24400,12 +24400,12 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:37Z</t>
+          <t>2026-08-24T05:47:50Z</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
@@ -24512,12 +24512,12 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:55Z</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
@@ -24624,12 +24624,12 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:55Z</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
@@ -24736,12 +24736,12 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:55Z</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
@@ -24848,12 +24848,12 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:55Z</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X221" t="inlineStr">
@@ -24960,12 +24960,12 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:55Z</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
@@ -25067,12 +25067,12 @@
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:40Z</t>
+          <t>2026-08-24T05:47:56Z</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
@@ -25179,12 +25179,12 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:55Z</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
@@ -25291,12 +25291,12 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:55Z</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
@@ -25403,12 +25403,12 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:56Z</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
@@ -25510,12 +25510,12 @@
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:56Z</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
@@ -25622,12 +25622,12 @@
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:56Z</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
@@ -25729,12 +25729,12 @@
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:56Z</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
@@ -25841,12 +25841,12 @@
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:56Z</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
@@ -25953,12 +25953,12 @@
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
@@ -26065,12 +26065,12 @@
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X232" t="inlineStr">
@@ -26167,12 +26167,12 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
@@ -26279,12 +26279,12 @@
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:41Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
@@ -26386,12 +26386,12 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:11Z</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X235" t="inlineStr">
@@ -26498,12 +26498,12 @@
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X236" t="inlineStr">
@@ -26615,12 +26615,12 @@
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:11Z</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X237" t="inlineStr">
@@ -26727,12 +26727,12 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X238" t="inlineStr">
@@ -26839,12 +26839,12 @@
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X239" t="inlineStr">
@@ -26946,12 +26946,12 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
@@ -27053,12 +27053,12 @@
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:10Z</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X241" t="inlineStr">
@@ -27165,12 +27165,12 @@
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:57Z</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
@@ -27277,12 +27277,12 @@
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
@@ -27389,12 +27389,12 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X244" t="inlineStr">
@@ -27506,12 +27506,12 @@
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:10Z</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
@@ -27618,12 +27618,12 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:47:59Z</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X246" t="inlineStr">
@@ -27725,12 +27725,12 @@
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
@@ -27837,12 +27837,12 @@
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X248" t="inlineStr">
@@ -27944,12 +27944,12 @@
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
@@ -28056,12 +28056,12 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X250" t="inlineStr">
@@ -28163,12 +28163,12 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:42Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
@@ -28275,12 +28275,12 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X252" t="inlineStr">
@@ -28382,12 +28382,12 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:47:58Z</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X253" t="inlineStr">
@@ -28494,12 +28494,12 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:47:59Z</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X254" t="inlineStr">
@@ -28606,12 +28606,12 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:47:59Z</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
@@ -28713,12 +28713,12 @@
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:47:59Z</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X256" t="inlineStr">
@@ -28825,12 +28825,12 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:00Z</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
@@ -28937,12 +28937,12 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:00Z</t>
         </is>
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X258" t="inlineStr">
@@ -29049,12 +29049,12 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:00Z</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
@@ -29146,12 +29146,12 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:55Z</t>
+          <t>2026-08-24T05:48:21Z</t>
         </is>
       </c>
       <c r="W260" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X260" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>3c57b6081ccc97b385fec25df685642ccdc0488564a22a59d5f05fbc9d717d9b</t>
+          <t>94a78c650ca2c95c07f89ba65971cde415dc6acbacf070d56c55a71042177929</t>
         </is>
       </c>
       <c r="Z260" t="inlineStr">
@@ -29253,12 +29253,12 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:00Z</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X261" t="inlineStr">
@@ -29365,12 +29365,12 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:00Z</t>
         </is>
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X262" t="inlineStr">
@@ -29472,12 +29472,12 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X263" t="inlineStr">
@@ -29584,12 +29584,12 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:00Z</t>
         </is>
       </c>
       <c r="W264" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X264" t="inlineStr">
@@ -29696,12 +29696,12 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:00Z</t>
         </is>
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X265" t="inlineStr">
@@ -29808,12 +29808,12 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X266" t="inlineStr">
@@ -29920,12 +29920,12 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X267" t="inlineStr">
@@ -30027,12 +30027,12 @@
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:43Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W268" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X268" t="inlineStr">
@@ -30139,12 +30139,12 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X269" t="inlineStr">
@@ -30251,12 +30251,12 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X270" t="inlineStr">
@@ -30358,12 +30358,12 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W271" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X271" t="inlineStr">
@@ -30465,12 +30465,12 @@
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X272" t="inlineStr">
@@ -30577,12 +30577,12 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X273" t="inlineStr">
@@ -30689,12 +30689,12 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:01Z</t>
         </is>
       </c>
       <c r="W274" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X274" t="inlineStr">
@@ -30801,12 +30801,12 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X275" t="inlineStr">
@@ -30913,12 +30913,12 @@
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W276" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X276" t="inlineStr">
@@ -31025,12 +31025,12 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:54Z</t>
+          <t>2026-08-24T05:48:22Z</t>
         </is>
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X277" t="inlineStr">
@@ -31137,12 +31137,12 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W278" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X278" t="inlineStr">
@@ -31244,12 +31244,12 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X279" t="inlineStr">
@@ -31356,12 +31356,12 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X280" t="inlineStr">
@@ -31468,12 +31468,12 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X281" t="inlineStr">
@@ -31580,12 +31580,12 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:44Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W282" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X282" t="inlineStr">
@@ -31687,12 +31687,12 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X283" t="inlineStr">
@@ -31799,12 +31799,12 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W284" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X284" t="inlineStr">
@@ -31906,12 +31906,12 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:02Z</t>
         </is>
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X285" t="inlineStr">
@@ -32018,12 +32018,12 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:03Z</t>
         </is>
       </c>
       <c r="W286" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X286" t="inlineStr">
@@ -32125,12 +32125,12 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:03Z</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X287" t="inlineStr">
@@ -32232,12 +32232,12 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:03Z</t>
         </is>
       </c>
       <c r="W288" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X288" t="inlineStr">
@@ -32344,12 +32344,12 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:03Z</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X289" t="inlineStr">
@@ -32456,12 +32456,12 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W290" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X290" t="inlineStr">
@@ -32568,12 +32568,12 @@
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X291" t="inlineStr">
@@ -32680,12 +32680,12 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X292" t="inlineStr">
@@ -32792,12 +32792,12 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X293" t="inlineStr">
@@ -32899,12 +32899,12 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:45Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W294" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X294" t="inlineStr">
@@ -33011,12 +33011,12 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X295" t="inlineStr">
@@ -33118,12 +33118,12 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W296" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X296" t="inlineStr">
@@ -33225,12 +33225,12 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X297" t="inlineStr">
@@ -33332,12 +33332,12 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W298" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X298" t="inlineStr">
@@ -33444,12 +33444,12 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
@@ -33556,12 +33556,12 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W300" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X300" t="inlineStr">
@@ -33668,12 +33668,12 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X301" t="inlineStr">
@@ -33780,12 +33780,12 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W302" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X302" t="inlineStr">
@@ -33887,12 +33887,12 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X303" t="inlineStr">
@@ -33999,12 +33999,12 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W304" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X304" t="inlineStr">
@@ -34111,12 +34111,12 @@
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X305" t="inlineStr">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W306" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X306" t="inlineStr">
@@ -34325,12 +34325,12 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:05Z</t>
         </is>
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X307" t="inlineStr">
@@ -34432,12 +34432,12 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:06Z</t>
         </is>
       </c>
       <c r="W308" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X308" t="inlineStr">
@@ -34539,12 +34539,12 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:06Z</t>
         </is>
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X309" t="inlineStr">
@@ -34646,12 +34646,12 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:06Z</t>
         </is>
       </c>
       <c r="W310" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X310" t="inlineStr">
@@ -34758,12 +34758,12 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:06Z</t>
         </is>
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X311" t="inlineStr">
@@ -34865,12 +34865,12 @@
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:06Z</t>
         </is>
       </c>
       <c r="W312" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X312" t="inlineStr">
@@ -34972,12 +34972,12 @@
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X313" t="inlineStr">
@@ -35084,12 +35084,12 @@
       </c>
       <c r="V314" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W314" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X314" t="inlineStr">
@@ -35196,12 +35196,12 @@
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W315" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X315" t="inlineStr">
@@ -35308,12 +35308,12 @@
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W316" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X316" t="inlineStr">
@@ -35415,12 +35415,12 @@
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X317" t="inlineStr">
@@ -35522,12 +35522,12 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W318" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X318" t="inlineStr">
@@ -35634,12 +35634,12 @@
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X319" t="inlineStr">
@@ -35746,12 +35746,12 @@
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W320" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X320" t="inlineStr">
@@ -35858,12 +35858,12 @@
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:07Z</t>
         </is>
       </c>
       <c r="W321" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X321" t="inlineStr">
@@ -35965,12 +35965,12 @@
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:47Z</t>
+          <t>2026-08-24T05:48:08Z</t>
         </is>
       </c>
       <c r="W322" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X322" t="inlineStr">
@@ -36077,12 +36077,12 @@
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:46Z</t>
+          <t>2026-08-24T05:48:04Z</t>
         </is>
       </c>
       <c r="W323" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X323" t="inlineStr">
@@ -36184,12 +36184,12 @@
       </c>
       <c r="V324" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:08Z</t>
         </is>
       </c>
       <c r="W324" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X324" t="inlineStr">
@@ -36296,12 +36296,12 @@
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:08Z</t>
         </is>
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X325" t="inlineStr">
@@ -36408,12 +36408,12 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W326" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X326" t="inlineStr">
@@ -36510,12 +36510,12 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W327" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X327" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W328" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X328" t="inlineStr">
@@ -36724,12 +36724,12 @@
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X329" t="inlineStr">
@@ -36831,12 +36831,12 @@
       </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W330" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X330" t="inlineStr">
@@ -36938,12 +36938,12 @@
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W331" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X331" t="inlineStr">
@@ -37045,12 +37045,12 @@
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W332" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X332" t="inlineStr">
@@ -37152,12 +37152,12 @@
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X333" t="inlineStr">
@@ -37259,12 +37259,12 @@
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:09Z</t>
         </is>
       </c>
       <c r="W334" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X334" t="inlineStr">
@@ -37361,12 +37361,12 @@
       </c>
       <c r="V335" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:48Z</t>
+          <t>2026-08-24T05:48:10Z</t>
         </is>
       </c>
       <c r="W335" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X335" t="inlineStr">
@@ -37473,12 +37473,12 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:10Z</t>
         </is>
       </c>
       <c r="W336" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X336" t="inlineStr">
@@ -37585,12 +37585,12 @@
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:10Z</t>
         </is>
       </c>
       <c r="W337" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X337" t="inlineStr">
@@ -37692,12 +37692,12 @@
       </c>
       <c r="V338" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W338" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X338" t="inlineStr">
@@ -37804,12 +37804,12 @@
       </c>
       <c r="V339" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W339" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X339" t="inlineStr">
@@ -37911,12 +37911,12 @@
       </c>
       <c r="V340" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W340" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X340" t="inlineStr">
@@ -38023,12 +38023,12 @@
       </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W341" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X341" t="inlineStr">
@@ -38130,12 +38130,12 @@
       </c>
       <c r="V342" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W342" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X342" t="inlineStr">
@@ -38242,12 +38242,12 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W343" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X343" t="inlineStr">
@@ -38349,12 +38349,12 @@
       </c>
       <c r="V344" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:11Z</t>
         </is>
       </c>
       <c r="W344" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X344" t="inlineStr">
@@ -38461,12 +38461,12 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W345" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X345" t="inlineStr">
@@ -38563,12 +38563,12 @@
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W346" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X346" t="inlineStr">
@@ -38675,12 +38675,12 @@
       </c>
       <c r="V347" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W347" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X347" t="inlineStr">
@@ -38787,12 +38787,12 @@
       </c>
       <c r="V348" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:49Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W348" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X348" t="inlineStr">
@@ -38894,12 +38894,12 @@
       </c>
       <c r="V349" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W349" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X349" t="inlineStr">
@@ -39006,12 +39006,12 @@
       </c>
       <c r="V350" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W350" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X350" t="inlineStr">
@@ -39113,12 +39113,12 @@
       </c>
       <c r="V351" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W351" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X351" t="inlineStr">
@@ -39225,12 +39225,12 @@
       </c>
       <c r="V352" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W352" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X352" t="inlineStr">
@@ -39337,12 +39337,12 @@
       </c>
       <c r="V353" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:12Z</t>
         </is>
       </c>
       <c r="W353" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X353" t="inlineStr">
@@ -39449,12 +39449,12 @@
       </c>
       <c r="V354" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:13Z</t>
         </is>
       </c>
       <c r="W354" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X354" t="inlineStr">
@@ -39561,12 +39561,12 @@
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W355" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X355" t="inlineStr">
@@ -39668,12 +39668,12 @@
       </c>
       <c r="V356" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W356" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X356" t="inlineStr">
@@ -39780,12 +39780,12 @@
       </c>
       <c r="V357" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:13Z</t>
         </is>
       </c>
       <c r="W357" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X357" t="inlineStr">
@@ -39892,12 +39892,12 @@
       </c>
       <c r="V358" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W358" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X358" t="inlineStr">
@@ -40004,12 +40004,12 @@
       </c>
       <c r="V359" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W359" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X359" t="inlineStr">
@@ -40116,12 +40116,12 @@
       </c>
       <c r="V360" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W360" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X360" t="inlineStr">
@@ -40228,12 +40228,12 @@
       </c>
       <c r="V361" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W361" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X361" t="inlineStr">
@@ -40340,12 +40340,12 @@
       </c>
       <c r="V362" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W362" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X362" t="inlineStr">
@@ -40452,12 +40452,12 @@
       </c>
       <c r="V363" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W363" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X363" t="inlineStr">
@@ -40564,12 +40564,12 @@
       </c>
       <c r="V364" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:50Z</t>
+          <t>2026-08-24T05:48:14Z</t>
         </is>
       </c>
       <c r="W364" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X364" t="inlineStr">
@@ -40676,12 +40676,12 @@
       </c>
       <c r="V365" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:15Z</t>
         </is>
       </c>
       <c r="W365" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X365" t="inlineStr">
@@ -40783,12 +40783,12 @@
       </c>
       <c r="V366" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:15Z</t>
         </is>
       </c>
       <c r="W366" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X366" t="inlineStr">
@@ -40895,12 +40895,12 @@
       </c>
       <c r="V367" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:15Z</t>
         </is>
       </c>
       <c r="W367" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X367" t="inlineStr">
@@ -41002,12 +41002,12 @@
       </c>
       <c r="V368" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:15Z</t>
         </is>
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X368" t="inlineStr">
@@ -41114,12 +41114,12 @@
       </c>
       <c r="V369" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W369" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X369" t="inlineStr">
@@ -41221,12 +41221,12 @@
       </c>
       <c r="V370" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W370" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X370" t="inlineStr">
@@ -41333,12 +41333,12 @@
       </c>
       <c r="V371" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W371" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X371" t="inlineStr">
@@ -41445,12 +41445,12 @@
       </c>
       <c r="V372" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W372" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X372" t="inlineStr">
@@ -41557,12 +41557,12 @@
       </c>
       <c r="V373" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W373" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X373" t="inlineStr">
@@ -41669,12 +41669,12 @@
       </c>
       <c r="V374" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X374" t="inlineStr">
@@ -41781,12 +41781,12 @@
       </c>
       <c r="V375" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W375" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X375" t="inlineStr">
@@ -41893,12 +41893,12 @@
       </c>
       <c r="V376" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:51Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W376" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X376" t="inlineStr">
@@ -42000,12 +42000,12 @@
       </c>
       <c r="V377" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W377" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X377" t="inlineStr">
@@ -42112,12 +42112,12 @@
       </c>
       <c r="V378" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:16Z</t>
         </is>
       </c>
       <c r="W378" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X378" t="inlineStr">
@@ -42224,12 +42224,12 @@
       </c>
       <c r="V379" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:17Z</t>
         </is>
       </c>
       <c r="W379" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X379" t="inlineStr">
@@ -42336,12 +42336,12 @@
       </c>
       <c r="V380" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:17Z</t>
         </is>
       </c>
       <c r="W380" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X380" t="inlineStr">
@@ -42448,12 +42448,12 @@
       </c>
       <c r="V381" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W381" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X381" t="inlineStr">
@@ -42560,12 +42560,12 @@
       </c>
       <c r="V382" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:17Z</t>
         </is>
       </c>
       <c r="W382" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X382" t="inlineStr">
@@ -42672,12 +42672,12 @@
       </c>
       <c r="V383" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:17Z</t>
         </is>
       </c>
       <c r="W383" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X383" t="inlineStr">
@@ -42784,12 +42784,12 @@
       </c>
       <c r="V384" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W384" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X384" t="inlineStr">
@@ -42896,12 +42896,12 @@
       </c>
       <c r="V385" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W385" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X385" t="inlineStr">
@@ -43008,12 +43008,12 @@
       </c>
       <c r="V386" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W386" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X386" t="inlineStr">
@@ -43115,12 +43115,12 @@
       </c>
       <c r="V387" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W387" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X387" t="inlineStr">
@@ -43227,12 +43227,12 @@
       </c>
       <c r="V388" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W388" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X388" t="inlineStr">
@@ -43339,12 +43339,12 @@
       </c>
       <c r="V389" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W389" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X389" t="inlineStr">
@@ -43446,12 +43446,12 @@
       </c>
       <c r="V390" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:18Z</t>
         </is>
       </c>
       <c r="W390" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X390" t="inlineStr">
@@ -43558,12 +43558,12 @@
       </c>
       <c r="V391" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W391" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X391" t="inlineStr">
@@ -43670,12 +43670,12 @@
       </c>
       <c r="V392" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W392" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X392" t="inlineStr">
@@ -43782,12 +43782,12 @@
       </c>
       <c r="V393" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:52Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W393" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X393" t="inlineStr">
@@ -43894,12 +43894,12 @@
       </c>
       <c r="V394" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W394" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X394" t="inlineStr">
@@ -44006,12 +44006,12 @@
       </c>
       <c r="V395" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W395" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X395" t="inlineStr">
@@ -44113,12 +44113,12 @@
       </c>
       <c r="V396" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W396" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X396" t="inlineStr">
@@ -44225,12 +44225,12 @@
       </c>
       <c r="V397" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:53Z</t>
+          <t>2026-08-24T05:48:19Z</t>
         </is>
       </c>
       <c r="W397" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X397" t="inlineStr">
@@ -44342,12 +44342,12 @@
       </c>
       <c r="V398" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:12Z</t>
+          <t>2026-08-24T05:47:11Z</t>
         </is>
       </c>
       <c r="W398" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X398" t="inlineStr">
@@ -44454,12 +44454,12 @@
       </c>
       <c r="V399" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W399" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X399" t="inlineStr">
@@ -44566,12 +44566,12 @@
       </c>
       <c r="V400" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:14Z</t>
+          <t>2026-08-24T05:47:13Z</t>
         </is>
       </c>
       <c r="W400" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X400" t="inlineStr">
@@ -44683,12 +44683,12 @@
       </c>
       <c r="V401" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W401" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X401" t="inlineStr">
@@ -44790,12 +44790,12 @@
       </c>
       <c r="V402" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W402" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X402" t="inlineStr">
@@ -44902,12 +44902,12 @@
       </c>
       <c r="V403" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W403" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X403" t="inlineStr">
@@ -45009,12 +45009,12 @@
       </c>
       <c r="V404" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W404" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X404" t="inlineStr">
@@ -45126,12 +45126,12 @@
       </c>
       <c r="V405" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W405" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X405" t="inlineStr">
@@ -45238,12 +45238,12 @@
       </c>
       <c r="V406" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W406" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X406" t="inlineStr">
@@ -45350,12 +45350,12 @@
       </c>
       <c r="V407" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W407" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X407" t="inlineStr">
@@ -45452,12 +45452,12 @@
       </c>
       <c r="V408" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W408" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X408" t="inlineStr">
@@ -45569,12 +45569,12 @@
       </c>
       <c r="V409" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W409" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X409" t="inlineStr">
@@ -45671,12 +45671,12 @@
       </c>
       <c r="V410" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:13Z</t>
+          <t>2026-08-24T05:47:12Z</t>
         </is>
       </c>
       <c r="W410" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X410" t="inlineStr">
@@ -45778,12 +45778,12 @@
       </c>
       <c r="V411" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:14Z</t>
+          <t>2026-08-24T05:47:13Z</t>
         </is>
       </c>
       <c r="W411" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X411" t="inlineStr">
@@ -45895,12 +45895,12 @@
       </c>
       <c r="V412" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:14Z</t>
+          <t>2026-08-24T05:47:13Z</t>
         </is>
       </c>
       <c r="W412" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X412" t="inlineStr">
@@ -46012,12 +46012,12 @@
       </c>
       <c r="V413" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:14Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W413" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X413" t="inlineStr">
@@ -46124,12 +46124,12 @@
       </c>
       <c r="V414" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:14Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W414" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X414" t="inlineStr">
@@ -46236,12 +46236,12 @@
       </c>
       <c r="V415" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X415" t="inlineStr">
@@ -46343,12 +46343,12 @@
       </c>
       <c r="V416" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:14Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W416" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X416" t="inlineStr">
@@ -46450,12 +46450,12 @@
       </c>
       <c r="V417" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W417" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X417" t="inlineStr">
@@ -46562,12 +46562,12 @@
       </c>
       <c r="V418" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W418" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X418" t="inlineStr">
@@ -46679,12 +46679,12 @@
       </c>
       <c r="V419" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W419" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X419" t="inlineStr">
@@ -46791,12 +46791,12 @@
       </c>
       <c r="V420" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W420" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X420" t="inlineStr">
@@ -46903,12 +46903,12 @@
       </c>
       <c r="V421" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:14Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W421" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X421" t="inlineStr">
@@ -47015,12 +47015,12 @@
       </c>
       <c r="V422" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W422" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X422" t="inlineStr">
@@ -47132,12 +47132,12 @@
       </c>
       <c r="V423" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W423" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X423" t="inlineStr">
@@ -47249,12 +47249,12 @@
       </c>
       <c r="V424" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:14Z</t>
         </is>
       </c>
       <c r="W424" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X424" t="inlineStr">
@@ -47361,12 +47361,12 @@
       </c>
       <c r="V425" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:15Z</t>
         </is>
       </c>
       <c r="W425" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X425" t="inlineStr">
@@ -47473,12 +47473,12 @@
       </c>
       <c r="V426" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:15Z</t>
         </is>
       </c>
       <c r="W426" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X426" t="inlineStr">
@@ -47585,12 +47585,12 @@
       </c>
       <c r="V427" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W427" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X427" t="inlineStr">
@@ -47692,12 +47692,12 @@
       </c>
       <c r="V428" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W428" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X428" t="inlineStr">
@@ -47804,12 +47804,12 @@
       </c>
       <c r="V429" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W429" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X429" t="inlineStr">
@@ -47921,12 +47921,12 @@
       </c>
       <c r="V430" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:15Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W430" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X430" t="inlineStr">
@@ -48023,12 +48023,12 @@
       </c>
       <c r="V431" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W431" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X431" t="inlineStr">
@@ -48140,12 +48140,12 @@
       </c>
       <c r="V432" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W432" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X432" t="inlineStr">
@@ -48252,12 +48252,12 @@
       </c>
       <c r="V433" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W433" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X433" t="inlineStr">
@@ -48359,12 +48359,12 @@
       </c>
       <c r="V434" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:16Z</t>
         </is>
       </c>
       <c r="W434" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X434" t="inlineStr">
@@ -48476,12 +48476,12 @@
       </c>
       <c r="V435" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W435" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X435" t="inlineStr">
@@ -48583,12 +48583,12 @@
       </c>
       <c r="V436" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W436" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X436" t="inlineStr">
@@ -48695,12 +48695,12 @@
       </c>
       <c r="V437" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W437" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X437" t="inlineStr">
@@ -48807,12 +48807,12 @@
       </c>
       <c r="V438" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W438" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X438" t="inlineStr">
@@ -48924,12 +48924,12 @@
       </c>
       <c r="V439" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W439" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X439" t="inlineStr">
@@ -49031,12 +49031,12 @@
       </c>
       <c r="V440" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W440" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X440" t="inlineStr">
@@ -49143,12 +49143,12 @@
       </c>
       <c r="V441" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W441" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X441" t="inlineStr">
@@ -49260,12 +49260,12 @@
       </c>
       <c r="V442" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W442" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X442" t="inlineStr">
@@ -49367,12 +49367,12 @@
       </c>
       <c r="V443" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:18Z</t>
         </is>
       </c>
       <c r="W443" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X443" t="inlineStr">
@@ -49484,12 +49484,12 @@
       </c>
       <c r="V444" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:18Z</t>
         </is>
       </c>
       <c r="W444" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X444" t="inlineStr">
@@ -49601,12 +49601,12 @@
       </c>
       <c r="V445" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:18Z</t>
         </is>
       </c>
       <c r="W445" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X445" t="inlineStr">
@@ -49708,12 +49708,12 @@
       </c>
       <c r="V446" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W446" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X446" t="inlineStr">
@@ -49815,12 +49815,12 @@
       </c>
       <c r="V447" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W447" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X447" t="inlineStr">
@@ -49932,12 +49932,12 @@
       </c>
       <c r="V448" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:18Z</t>
         </is>
       </c>
       <c r="W448" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X448" t="inlineStr">
@@ -50049,12 +50049,12 @@
       </c>
       <c r="V449" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W449" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X449" t="inlineStr">
@@ -50151,12 +50151,12 @@
       </c>
       <c r="V450" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:17Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W450" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X450" t="inlineStr">
@@ -50263,12 +50263,12 @@
       </c>
       <c r="V451" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W451" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X451" t="inlineStr">
@@ -50380,12 +50380,12 @@
       </c>
       <c r="V452" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W452" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X452" t="inlineStr">
@@ -50497,12 +50497,12 @@
       </c>
       <c r="V453" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W453" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X453" t="inlineStr">
@@ -50609,12 +50609,12 @@
       </c>
       <c r="V454" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W454" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X454" t="inlineStr">
@@ -50721,12 +50721,12 @@
       </c>
       <c r="V455" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W455" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X455" t="inlineStr">
@@ -50833,12 +50833,12 @@
       </c>
       <c r="V456" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W456" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X456" t="inlineStr">
@@ -50945,12 +50945,12 @@
       </c>
       <c r="V457" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:19Z</t>
         </is>
       </c>
       <c r="W457" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X457" t="inlineStr">
@@ -51052,12 +51052,12 @@
       </c>
       <c r="V458" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:20Z</t>
         </is>
       </c>
       <c r="W458" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X458" t="inlineStr">
@@ -51169,12 +51169,12 @@
       </c>
       <c r="V459" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:20Z</t>
         </is>
       </c>
       <c r="W459" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X459" t="inlineStr">
@@ -51276,12 +51276,12 @@
       </c>
       <c r="V460" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W460" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X460" t="inlineStr">
@@ -51383,12 +51383,12 @@
       </c>
       <c r="V461" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:16Z</t>
+          <t>2026-08-24T05:47:17Z</t>
         </is>
       </c>
       <c r="W461" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X461" t="inlineStr">
@@ -51495,12 +51495,12 @@
       </c>
       <c r="V462" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:20Z</t>
         </is>
       </c>
       <c r="W462" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X462" t="inlineStr">
@@ -51612,12 +51612,12 @@
       </c>
       <c r="V463" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W463" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X463" t="inlineStr">
@@ -51729,12 +51729,12 @@
       </c>
       <c r="V464" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:20Z</t>
         </is>
       </c>
       <c r="W464" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X464" t="inlineStr">
@@ -51831,12 +51831,12 @@
       </c>
       <c r="V465" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W465" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X465" t="inlineStr">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="V466" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:20Z</t>
         </is>
       </c>
       <c r="W466" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X466" t="inlineStr">
@@ -52060,12 +52060,12 @@
       </c>
       <c r="V467" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:18Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W467" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X467" t="inlineStr">
@@ -52177,12 +52177,12 @@
       </c>
       <c r="V468" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W468" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X468" t="inlineStr">
@@ -52284,12 +52284,12 @@
       </c>
       <c r="V469" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W469" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X469" t="inlineStr">
@@ -52396,12 +52396,12 @@
       </c>
       <c r="V470" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:21Z</t>
         </is>
       </c>
       <c r="W470" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X470" t="inlineStr">
@@ -52508,12 +52508,12 @@
       </c>
       <c r="V471" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W471" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X471" t="inlineStr">
@@ -52615,12 +52615,12 @@
       </c>
       <c r="V472" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W472" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X472" t="inlineStr">
@@ -52727,12 +52727,12 @@
       </c>
       <c r="V473" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W473" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X473" t="inlineStr">
@@ -52839,12 +52839,12 @@
       </c>
       <c r="V474" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W474" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X474" t="inlineStr">
@@ -52946,12 +52946,12 @@
       </c>
       <c r="V475" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W475" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X475" t="inlineStr">
@@ -53058,12 +53058,12 @@
       </c>
       <c r="V476" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W476" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X476" t="inlineStr">
@@ -53170,12 +53170,12 @@
       </c>
       <c r="V477" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W477" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X477" t="inlineStr">
@@ -53282,12 +53282,12 @@
       </c>
       <c r="V478" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W478" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X478" t="inlineStr">
@@ -53394,12 +53394,12 @@
       </c>
       <c r="V479" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:23Z</t>
         </is>
       </c>
       <c r="W479" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X479" t="inlineStr">
@@ -53511,12 +53511,12 @@
       </c>
       <c r="V480" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:23Z</t>
         </is>
       </c>
       <c r="W480" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X480" t="inlineStr">
@@ -53628,12 +53628,12 @@
       </c>
       <c r="V481" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:23Z</t>
         </is>
       </c>
       <c r="W481" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X481" t="inlineStr">
@@ -53730,12 +53730,12 @@
       </c>
       <c r="V482" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:23Z</t>
+          <t>2026-08-24T05:47:28Z</t>
         </is>
       </c>
       <c r="W482" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X482" t="inlineStr">
@@ -53847,12 +53847,12 @@
       </c>
       <c r="V483" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:19Z</t>
+          <t>2026-08-24T05:47:22Z</t>
         </is>
       </c>
       <c r="W483" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X483" t="inlineStr">
@@ -53959,12 +53959,12 @@
       </c>
       <c r="V484" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W484" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X484" t="inlineStr">
@@ -54076,12 +54076,12 @@
       </c>
       <c r="V485" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W485" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X485" t="inlineStr">
@@ -54188,12 +54188,12 @@
       </c>
       <c r="V486" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W486" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X486" t="inlineStr">
@@ -54305,12 +54305,12 @@
       </c>
       <c r="V487" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W487" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X487" t="inlineStr">
@@ -54422,12 +54422,12 @@
       </c>
       <c r="V488" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W488" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X488" t="inlineStr">
@@ -54539,12 +54539,12 @@
       </c>
       <c r="V489" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W489" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X489" t="inlineStr">
@@ -54651,12 +54651,12 @@
       </c>
       <c r="V490" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W490" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X490" t="inlineStr">
@@ -54763,12 +54763,12 @@
       </c>
       <c r="V491" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:20Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W491" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X491" t="inlineStr">
@@ -54865,12 +54865,12 @@
       </c>
       <c r="V492" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:24Z</t>
         </is>
       </c>
       <c r="W492" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X492" t="inlineStr">
@@ -54977,12 +54977,12 @@
       </c>
       <c r="V493" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:25Z</t>
         </is>
       </c>
       <c r="W493" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X493" t="inlineStr">
@@ -55079,12 +55079,12 @@
       </c>
       <c r="V494" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:25Z</t>
         </is>
       </c>
       <c r="W494" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X494" t="inlineStr">
@@ -55191,12 +55191,12 @@
       </c>
       <c r="V495" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:25Z</t>
         </is>
       </c>
       <c r="W495" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X495" t="inlineStr">
@@ -55308,12 +55308,12 @@
       </c>
       <c r="V496" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:25Z</t>
         </is>
       </c>
       <c r="W496" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X496" t="inlineStr">
@@ -55420,12 +55420,12 @@
       </c>
       <c r="V497" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:25Z</t>
         </is>
       </c>
       <c r="W497" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X497" t="inlineStr">
@@ -55537,12 +55537,12 @@
       </c>
       <c r="V498" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:25Z</t>
         </is>
       </c>
       <c r="W498" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X498" t="inlineStr">
@@ -55649,12 +55649,12 @@
       </c>
       <c r="V499" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:25Z</t>
         </is>
       </c>
       <c r="W499" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X499" t="inlineStr">
@@ -55756,12 +55756,12 @@
       </c>
       <c r="V500" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:21Z</t>
+          <t>2026-08-24T05:47:26Z</t>
         </is>
       </c>
       <c r="W500" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X500" t="inlineStr">
@@ -55863,12 +55863,12 @@
       </c>
       <c r="V501" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:26Z</t>
         </is>
       </c>
       <c r="W501" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X501" t="inlineStr">
@@ -55975,12 +55975,12 @@
       </c>
       <c r="V502" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:26Z</t>
         </is>
       </c>
       <c r="W502" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X502" t="inlineStr">
@@ -56092,12 +56092,12 @@
       </c>
       <c r="V503" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:26Z</t>
         </is>
       </c>
       <c r="W503" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X503" t="inlineStr">
@@ -56204,12 +56204,12 @@
       </c>
       <c r="V504" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:26Z</t>
         </is>
       </c>
       <c r="W504" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X504" t="inlineStr">
@@ -56311,12 +56311,12 @@
       </c>
       <c r="V505" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W505" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X505" t="inlineStr">
@@ -56423,12 +56423,12 @@
       </c>
       <c r="V506" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W506" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X506" t="inlineStr">
@@ -56535,12 +56535,12 @@
       </c>
       <c r="V507" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W507" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X507" t="inlineStr">
@@ -56652,12 +56652,12 @@
       </c>
       <c r="V508" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W508" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X508" t="inlineStr">
@@ -56764,12 +56764,12 @@
       </c>
       <c r="V509" t="inlineStr">
         <is>
-          <t>2026-08-24T05:20:22Z</t>
+          <t>2026-08-24T05:47:27Z</t>
         </is>
       </c>
       <c r="W509" t="inlineStr">
         <is>
-          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.0</t>
+          <t>household-expo-autumn-2026-official-catalog-signo-v1.0.1</t>
         </is>
       </c>
       <c r="X509" t="inlineStr">
